--- a/ML-Entrees/ig/StructureDefinition-fr-lm-attachement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-attachement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="160">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-attachement.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-attachement.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-attachement.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-attachement.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-attachement.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-attachement.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-attachement.header.source</t>
+    <t>fr-lm-attachement.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -412,60 +454,62 @@
     <t>fr-lm-entry.header.langue</t>
   </si>
   <si>
-    <t>fr-lm-attachement.code</t>
-  </si>
-  <si>
-    <t>Code de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.statut</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.typeDocumentAttache</t>
-  </si>
-  <si>
-    <t>Type de document attaché</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.typeDocumentAttache.natureDocument</t>
-  </si>
-  <si>
-    <t>Nature du document</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.documentAttache</t>
-  </si>
-  <si>
-    <t>Bloc document attaché</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.documentAttache.observationMedia</t>
-  </si>
-  <si>
-    <t>Observation média</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.documentAttache.observationMedia.identifiant</t>
-  </si>
-  <si>
-    <t>Identifiant de l’observationMedia</t>
-  </si>
-  <si>
-    <t>fr-lm-attachement.documentAttache.observationMedia.documentAttacheEncode</t>
+    <t>fr-lm-attachement.contentType</t>
+  </si>
+  <si>
+    <t>Type MIME de la piece jointe, avec encodage de caracteres, etc.</t>
+  </si>
+  <si>
+    <t>(preferred): BCP-13</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.language</t>
+  </si>
+  <si>
+    <t>Langue du contenu</t>
+  </si>
+  <si>
+    <t>(preferred): BCP 47</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.data</t>
   </si>
   <si>
     <t xml:space="preserve">base64Binary
 </t>
   </si>
   <si>
-    <t>Document attaché encodé en Base64</t>
+    <t>Contenu encode en base64</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>URL de la ressource</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Taille de la piece jointe avant encodage en base64</t>
+  </si>
+  <si>
+    <t>fr-lm-attachement.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Titre de la piece jointe</t>
   </si>
 </sst>
 </file>
@@ -767,11 +811,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="64.64453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="64.64453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="51.625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="51.625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -780,7 +824,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -794,14 +838,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.58203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="64.64453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1545,13 +1589,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1602,7 +1646,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1619,10 +1663,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1645,13 +1689,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1702,7 +1746,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1719,10 +1763,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1745,13 +1789,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1802,7 +1846,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1819,10 +1863,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1845,7 +1889,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -1945,13 +1989,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2002,7 +2046,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2019,10 +2063,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2033,7 +2077,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2045,13 +2089,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2102,13 +2146,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2119,10 +2163,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2133,7 +2177,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2145,13 +2189,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2202,13 +2246,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2219,10 +2263,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2233,7 +2277,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2245,13 +2289,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2302,13 +2346,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2319,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2330,7 +2374,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2345,13 +2389,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2402,10 +2446,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2481,10 +2525,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2502,7 +2546,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2519,10 +2563,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2530,7 +2574,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2545,13 +2589,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2602,10 +2646,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2619,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2630,7 +2674,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2645,13 +2689,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2702,10 +2746,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2719,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2730,7 +2774,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2745,13 +2789,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2781,7 +2825,7 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Z20" t="s" s="2">
         <v>73</v>
@@ -2802,10 +2846,10 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -2819,10 +2863,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2830,7 +2874,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2845,13 +2889,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2881,7 +2925,7 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>73</v>
@@ -2902,10 +2946,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2919,10 +2963,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2930,7 +2974,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -2945,13 +2989,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3002,10 +3046,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3019,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3030,7 +3074,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3045,13 +3089,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3102,10 +3146,10 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3114,6 +3158,206 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-attachement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-attachement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-attachement.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-attachement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
